--- a/corona-server-side-asp.net/Excels/Sections/מבט על/מתחסנים.xlsx
+++ b/corona-server-side-asp.net/Excels/Sections/מבט על/מתחסנים.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>מנה 1</t>
   </si>
@@ -43,6 +43,24 @@
   </si>
   <si>
     <t>group</t>
+  </si>
+  <si>
+    <t>keyEnglish</t>
+  </si>
+  <si>
+    <t>dose 1</t>
+  </si>
+  <si>
+    <t>dose 2</t>
+  </si>
+  <si>
+    <t>dose 3</t>
+  </si>
+  <si>
+    <t>dose 4</t>
+  </si>
+  <si>
+    <t>Omicron</t>
   </si>
 </sst>
 </file>
@@ -86,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +116,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -385,60 +404,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3">
+      <c r="D2" s="3">
         <v>6725362</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3">
+      <c r="D3" s="3">
         <v>6144955</v>
       </c>
       <c r="G3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="3">
+      <c r="D4" s="3">
         <v>4467842</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4">
+      <c r="D5" s="4">
         <v>836359</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4">
+      <c r="D6" s="4">
         <v>407548</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>